--- a/Indicadores.xlsx
+++ b/Indicadores.xlsx
@@ -492,13 +492,13 @@
         <v>1.7</v>
       </c>
       <c r="E4" s="1">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F4" s="1">
         <v>1.8</v>
       </c>
       <c r="G4" s="1">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -534,22 +534,22 @@
         <v>1470</v>
       </c>
       <c r="B8">
-        <v>1498</v>
+        <v>1512</v>
       </c>
       <c r="C8">
-        <v>1531</v>
+        <v>1546</v>
       </c>
       <c r="D8">
-        <v>1564</v>
+        <v>1577</v>
       </c>
       <c r="E8">
-        <v>1593</v>
+        <v>1618</v>
       </c>
       <c r="F8">
-        <v>1621</v>
+        <v>1652</v>
       </c>
       <c r="G8">
-        <v>1766</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -585,22 +585,22 @@
         <v>22.5</v>
       </c>
       <c r="B12" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="C12" s="1">
+        <v>22.72</v>
+      </c>
+      <c r="D12" s="1">
         <v>22.3</v>
-      </c>
-      <c r="C12" s="1">
-        <v>22.53</v>
-      </c>
-      <c r="D12" s="1">
-        <v>22.47</v>
       </c>
       <c r="E12" s="1">
         <v>22.1</v>
       </c>
       <c r="F12" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="G12" s="1">
         <v>22</v>
-      </c>
-      <c r="G12" s="1">
-        <v>20.75</v>
       </c>
     </row>
   </sheetData>

--- a/Indicadores.xlsx
+++ b/Indicadores.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
   <si>
     <t>Julio</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Diciembre</t>
+  </si>
+  <si>
+    <t>Enero</t>
   </si>
 </sst>
 </file>
@@ -447,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19417159-0C2D-4FF1-A703-3FC408462AE5}">
-  <dimension ref="A2:G12"/>
+  <dimension ref="A2:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -455,7 +458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -475,10 +478,13 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -498,6 +504,9 @@
         <v>1.8</v>
       </c>
       <c r="G4" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="H4" s="1">
         <v>21.8</v>
       </c>
     </row>
@@ -506,7 +515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -526,10 +535,13 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1470</v>
       </c>
@@ -549,6 +561,9 @@
         <v>1652</v>
       </c>
       <c r="G8">
+        <v>1688</v>
+      </c>
+      <c r="H8">
         <v>1859</v>
       </c>
     </row>
@@ -557,7 +572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -577,10 +592,13 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>22.5</v>
       </c>
@@ -600,6 +618,9 @@
         <v>22.2</v>
       </c>
       <c r="G12" s="1">
+        <v>22.1</v>
+      </c>
+      <c r="H12" s="1">
         <v>22</v>
       </c>
     </row>

--- a/Indicadores.xlsx
+++ b/Indicadores.xlsx
@@ -1,101 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franciscogranda/Desktop/Balanz/Monitores AI/Monitor Renta Fija ARG/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99417B1-AD27-924B-AA2E-2147A57C137C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="19420" windowHeight="10420" xr2:uid="{2A1DE20B-9174-463B-B235-59454B6DEAC4}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="19420" windowHeight="10420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Indicadores" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
-  <si>
-    <t>Julio</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>12 Meses</t>
-  </si>
-  <si>
-    <t>Octubre</t>
-  </si>
-  <si>
-    <t>Septiembre</t>
-  </si>
-  <si>
-    <t>REM inflación</t>
-  </si>
-  <si>
-    <t>REM tipo de cambio</t>
-  </si>
-  <si>
-    <t>Noviembre</t>
-  </si>
-  <si>
-    <t>REM tamar</t>
-  </si>
-  <si>
-    <t>Diciembre</t>
-  </si>
-  <si>
-    <t>Enero</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -114,22 +52,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -449,178 +446,197 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19417159-0C2D-4FF1-A703-3FC408462AE5}">
-  <dimension ref="A2:H12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>5</v>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12 Meses</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>21.8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="H4" s="1">
-        <v>21.8</v>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>12 Meses</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>6</v>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1546</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1577</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1618</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1652</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1688</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1859</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" t="s">
-        <v>2</v>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>12 Meses</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1470</v>
-      </c>
-      <c r="B8">
-        <v>1512</v>
-      </c>
-      <c r="C8">
-        <v>1546</v>
-      </c>
-      <c r="D8">
-        <v>1577</v>
-      </c>
-      <c r="E8">
-        <v>1618</v>
-      </c>
-      <c r="F8">
-        <v>1652</v>
-      </c>
-      <c r="G8">
-        <v>1688</v>
-      </c>
-      <c r="H8">
-        <v>1859</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="12">
+      <c r="A12" s="1" t="n">
         <v>22.4</v>
       </c>
-      <c r="C12" s="1">
+      <c r="B12" s="1" t="n">
         <v>22.72</v>
       </c>
-      <c r="D12" s="1">
+      <c r="C12" s="1" t="n">
         <v>22.3</v>
       </c>
-      <c r="E12" s="1">
+      <c r="D12" s="1" t="n">
         <v>22.1</v>
       </c>
-      <c r="F12" s="1">
+      <c r="E12" s="1" t="n">
         <v>22.2</v>
       </c>
-      <c r="G12" s="1">
+      <c r="F12" s="1" t="n">
         <v>22.1</v>
       </c>
-      <c r="H12" s="1">
+      <c r="G12" s="1" t="n">
         <v>22</v>
       </c>
     </row>

--- a/Indicadores.xlsx
+++ b/Indicadores.xlsx
@@ -451,11 +451,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A2:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REM inflación</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -515,9 +520,15 @@
       <c r="G4" s="1" t="n">
         <v>21.8</v>
       </c>
-    </row>
-    <row r="5"/>
-    <row r="6"/>
+      <c r="H4" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REM tipo de cambio</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -578,8 +589,13 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REM tamar</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -639,6 +655,7 @@
       <c r="G12" s="1" t="n">
         <v>22</v>
       </c>
+      <c r="H12" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Indicadores.xlsx
+++ b/Indicadores.xlsx
@@ -500,7 +500,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1.8</v>
@@ -512,13 +512,13 @@
         <v>1.6</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="H4" s="1" t="n"/>
     </row>
@@ -532,32 +532,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Diciembre</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Diciembre</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -568,25 +568,25 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1512</v>
+        <v>1530.4</v>
       </c>
       <c r="B8" t="n">
-        <v>1546</v>
+        <v>1565</v>
       </c>
       <c r="C8" t="n">
-        <v>1577</v>
+        <v>1600</v>
       </c>
       <c r="D8" t="n">
-        <v>1618</v>
+        <v>1629.6</v>
       </c>
       <c r="E8" t="n">
-        <v>1652</v>
+        <v>1661.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1688</v>
+        <v>1695</v>
       </c>
       <c r="G8" t="n">
-        <v>1859</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="10">
@@ -599,32 +599,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Diciembre</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Diciembre</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -635,25 +635,25 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>22.4</v>
+        <v>24.11</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>22.72</v>
+        <v>23.8</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>22.3</v>
+        <v>23.26</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>22.1</v>
+        <v>23.45</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>22</v>
+        <v>24.71</v>
       </c>
       <c r="H12" s="1" t="n"/>
     </row>

--- a/Indicadores.xlsx
+++ b/Indicadores.xlsx
@@ -500,7 +500,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1.8</v>

--- a/Indicadores.xlsx
+++ b/Indicadores.xlsx
@@ -464,32 +464,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Agosto</t>
+          <t>Septiembre</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Septiembre</t>
+          <t>Octubre</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Octubre</t>
+          <t>Noviembre</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Noviembre</t>
+          <t>Diciembre</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Diciembre</t>
+          <t>Enero</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enero</t>
+          <t>Febrero</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -500,19 +500,19 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>1.7</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>1.8</v>
-      </c>
       <c r="C4" s="1" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>1.6</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>1.78</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1.6</v>
